--- a/idc_manifests.xlsx
+++ b/idc_manifests.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rutherfordmichaelw\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uams.sharepoint.com/sites/Work8/Shared Documents/General/Code/posda-nextjs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC682693-820C-4F41-81F3-CD57EB1B9A21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="57" documentId="13_ncr:1_{BC682693-820C-4F41-81F3-CD57EB1B9A21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{01A8AFEA-69A9-4FE5-AB70-37B6F5D1F284}"/>
   <bookViews>
-    <workbookView xWindow="9870" yWindow="1545" windowWidth="18930" windowHeight="13395" xr2:uid="{B8C132A8-06DD-4852-87E5-07B83CF61F4D}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{B8C132A8-06DD-4852-87E5-07B83CF61F4D}"/>
   </bookViews>
   <sheets>
     <sheet name="dataset" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="clinical" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -38,35 +39,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="41">
-  <si>
-    <t>title</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="84">
   <si>
     <t>source_doi</t>
   </si>
   <si>
-    <t>source_url</t>
-  </si>
-  <si>
     <t>program</t>
   </si>
   <si>
-    <t>license_url</t>
-  </si>
-  <si>
-    <t>License URL</t>
-  </si>
-  <si>
-    <t>license_long_name</t>
-  </si>
-  <si>
-    <t>License long name</t>
-  </si>
-  <si>
-    <t>license_short_name</t>
-  </si>
-  <si>
     <t>abstract</t>
   </si>
   <si>
@@ -76,21 +56,9 @@
     <t>citation</t>
   </si>
   <si>
-    <t>TCIA collection version citation </t>
-  </si>
-  <si>
     <t>manager/collections/{post_id} or manager/analysis-results/{post_id}</t>
   </si>
   <si>
-    <t>status</t>
-  </si>
-  <si>
-    <t>updated</t>
-  </si>
-  <si>
-    <t>version</t>
-  </si>
-  <si>
     <t>cancer_type</t>
   </si>
   <si>
@@ -127,9 +95,6 @@
     <t>cancer_locations</t>
   </si>
   <si>
-    <t>name</t>
-  </si>
-  <si>
     <t>type</t>
   </si>
   <si>
@@ -161,6 +126,171 @@
   </si>
   <si>
     <t>collection_doi or result_doi</t>
+  </si>
+  <si>
+    <t>TCIA collection DOI</t>
+  </si>
+  <si>
+    <t>collection_title or result_title</t>
+  </si>
+  <si>
+    <t>post_id</t>
+  </si>
+  <si>
+    <t>Need to collection and fill from NBIA</t>
+  </si>
+  <si>
+    <t>todo</t>
+  </si>
+  <si>
+    <t>dataset short name</t>
+  </si>
+  <si>
+    <t>dataset title</t>
+  </si>
+  <si>
+    <t>dataset status (complete, ongoing)</t>
+  </si>
+  <si>
+    <t>dataset version date</t>
+  </si>
+  <si>
+    <t>dataset version number</t>
+  </si>
+  <si>
+    <t>dataset doi</t>
+  </si>
+  <si>
+    <t>dataset url</t>
+  </si>
+  <si>
+    <t>cancer types represented in dataset</t>
+  </si>
+  <si>
+    <t>supporting data in found in collection</t>
+  </si>
+  <si>
+    <t>species represented in collection</t>
+  </si>
+  <si>
+    <t>cancer location represented in collection</t>
+  </si>
+  <si>
+    <t>program (community, etc)</t>
+  </si>
+  <si>
+    <t>citations</t>
+  </si>
+  <si>
+    <t>Lookup ids and find citation with citation_type "Data Citation"</t>
+  </si>
+  <si>
+    <t>recordset_type</t>
+  </si>
+  <si>
+    <t>Collection or analysis result</t>
+  </si>
+  <si>
+    <t>recordset_hash</t>
+  </si>
+  <si>
+    <t>MD5 hash of the concatenation of the patient hashes ordered by hash.</t>
+  </si>
+  <si>
+    <t>recordset_name</t>
+  </si>
+  <si>
+    <t>The collection or analysis result name</t>
+  </si>
+  <si>
+    <t>—-instances—-</t>
+  </si>
+  <si>
+    <t>collection_name</t>
+  </si>
+  <si>
+    <t>TCIA collection (or analysis result) short name</t>
+  </si>
+  <si>
+    <t>patient_id</t>
+  </si>
+  <si>
+    <t>DICOM Patient identifier</t>
+  </si>
+  <si>
+    <t>patient_hash</t>
+  </si>
+  <si>
+    <t>MD5 hash of the concatenation of the study hashes ordered by hash.</t>
+  </si>
+  <si>
+    <t>study_instance_uid</t>
+  </si>
+  <si>
+    <t>DICOM Study instance UID</t>
+  </si>
+  <si>
+    <t>study_hash</t>
+  </si>
+  <si>
+    <t>MD5 hash of the concatenation of the series hashes ordered by hash.</t>
+  </si>
+  <si>
+    <t>series_instance_uid</t>
+  </si>
+  <si>
+    <t>DICOM Series instance UID</t>
+  </si>
+  <si>
+    <t>series_hash</t>
+  </si>
+  <si>
+    <t>MD5 hash of the concatenation of the instance hashes ordered by hash.</t>
+  </si>
+  <si>
+    <t>sop_instance_uid</t>
+  </si>
+  <si>
+    <t>DICOM SOP instance UID</t>
+  </si>
+  <si>
+    <t>instance_hash</t>
+  </si>
+  <si>
+    <t>MD5 hash of the DICOM instance</t>
+  </si>
+  <si>
+    <t>gcs_url</t>
+  </si>
+  <si>
+    <t>Google Cloud Services bucket</t>
+  </si>
+  <si>
+    <t>dataset_slug</t>
+  </si>
+  <si>
+    <t>dataset_type</t>
+  </si>
+  <si>
+    <t>dataset_doi</t>
+  </si>
+  <si>
+    <t>dataset_short_name</t>
+  </si>
+  <si>
+    <t>dataset_title</t>
+  </si>
+  <si>
+    <t>dataset_status</t>
+  </si>
+  <si>
+    <t>dataset_version</t>
+  </si>
+  <si>
+    <t>dataset_version_date</t>
+  </si>
+  <si>
+    <t>dataset_url</t>
   </si>
 </sst>
 </file>
@@ -196,7 +326,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -204,15 +334,36 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -229,6 +380,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -548,244 +703,272 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1BBF4B6-E74D-4627-965A-D3168AC43FAF}">
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr defaultColWidth="54.3828125" defaultRowHeight="14.15" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="26.3046875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="33.69140625" style="1" customWidth="1"/>
     <col min="2" max="2" width="62.765625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="38.07421875" style="1" customWidth="1"/>
-    <col min="4" max="16384" width="54.3828125" style="1"/>
+    <col min="3" max="3" width="43.765625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="55.84375" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="54.3828125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D1" s="1" t="s">
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B2" s="2" t="s">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D3" s="1" t="s">
+      <c r="D9" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" s="1" t="s">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A16" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E17" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A17" s="2" t="s">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A18" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="B18" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A20" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A21" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>12</v>
+        <v>5</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -795,9 +978,152 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DE1AFB8-D1A2-4D55-AF9F-D2644AB4457B}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
-  <sheetData/>
+  <dimension ref="A1:B20"/>
+  <sheetFormatPr defaultColWidth="103.15234375" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="18.69140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="65.3828125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A3" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+    </row>
+    <row r="5" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
+    </row>
+    <row r="6" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A6" s="3"/>
+      <c r="B6" s="3"/>
+    </row>
+    <row r="7" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
+    </row>
+    <row r="8" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A8" s="3"/>
+      <c r="B8" s="3"/>
+    </row>
+    <row r="9" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A9" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B9" s="4"/>
+    </row>
+    <row r="10" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A10" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A11" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A12" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A13" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A15" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A16" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A17" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A19" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A20" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -812,6 +1138,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e27ea474-41bf-44b2-987b-afb00d563621">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="629dd35a-14bc-4f22-ab23-66093791c42c" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010013EA0B3E190F5A4E980D9F1A6CD3F6D2" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="730feec53ea10df3f184fd0a69278d35">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e27ea474-41bf-44b2-987b-afb00d563621" xmlns:ns3="629dd35a-14bc-4f22-ab23-66093791c42c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="bd8361d7663be46d399f1053d5e95d30" ns2:_="" ns3:_="">
     <xsd:import namespace="e27ea474-41bf-44b2-987b-afb00d563621"/>
@@ -1006,7 +1343,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -1015,25 +1352,40 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e27ea474-41bf-44b2-987b-afb00d563621">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="629dd35a-14bc-4f22-ab23-66093791c42c" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D21C4B50-CEC4-4C9E-8625-DD0BD19CBF66}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{943DDC90-96A9-49BA-8F2A-7C001B5A02E1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="e27ea474-41bf-44b2-987b-afb00d563621"/>
+    <ds:schemaRef ds:uri="629dd35a-14bc-4f22-ab23-66093791c42c"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6F5941A7-6370-495E-849D-ADD90FA9C7CF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D21C4B50-CEC4-4C9E-8625-DD0BD19CBF66}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="e27ea474-41bf-44b2-987b-afb00d563621"/>
+    <ds:schemaRef ds:uri="629dd35a-14bc-4f22-ab23-66093791c42c"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{943DDC90-96A9-49BA-8F2A-7C001B5A02E1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6F5941A7-6370-495E-849D-ADD90FA9C7CF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>